--- a/artfynd/A 54601-2022 artfynd.xlsx
+++ b/artfynd/A 54601-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,32 +799,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97700240</v>
+        <v>137398924</v>
       </c>
       <c r="B3" t="n">
-        <v>91907</v>
+        <v>92969</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1110</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,14 +841,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brotorpsskogen, Hummelstad, Sm</t>
+          <t>Brotorp, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575780</v>
+        <v>575763</v>
       </c>
       <c r="R3" t="n">
-        <v>6404610</v>
+        <v>6404664</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,12 +875,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,41 +907,45 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97700240</t>
+          <t>https://artportalen.se/Sighting/137398924</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105804970</v>
+        <v>97700240</v>
       </c>
       <c r="B4" t="n">
-        <v>91909</v>
+        <v>91907</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1110</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Pers.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -951,14 +955,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 54601, Brotorp, Sm</t>
+          <t>Brotorpsskogen, Hummelstad, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575628</v>
+        <v>575780</v>
       </c>
       <c r="R4" t="n">
-        <v>6404582</v>
+        <v>6404610</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,17 +989,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-01-06</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-01-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På undersidan/sidan av granlåga</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,16 +1021,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105804970</t>
+          <t>https://artportalen.se/Sighting/97700240</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111837758</v>
+        <v>105804970</v>
       </c>
       <c r="B5" t="n">
-        <v>92732</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,28 +1038,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2014</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1070,14 +1065,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brotorp, hyggeskant, Sm</t>
+          <t>A 54601, Brotorp, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575674</v>
+        <v>575628</v>
       </c>
       <c r="R5" t="n">
-        <v>6404513</v>
+        <v>6404582</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,17 +1099,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-01-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-01-06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På asplåga.</t>
+          <t>På undersidan/sidan av granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,16 +1136,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111837758</t>
+          <t>https://artportalen.se/Sighting/105804970</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111837741</v>
+        <v>111837758</v>
       </c>
       <c r="B6" t="n">
-        <v>93189</v>
+        <v>92732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,26 +1153,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>2014</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1193,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575654</v>
+        <v>575674</v>
       </c>
       <c r="R6" t="n">
-        <v>6404507</v>
+        <v>6404513</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,6 +1226,11 @@
           <t>2023-09-01</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På asplåga.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1255,43 +1255,43 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111837741</t>
+          <t>https://artportalen.se/Sighting/111837758</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111837705</v>
+        <v>111837741</v>
       </c>
       <c r="B7" t="n">
-        <v>93193</v>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4363</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1303,14 +1303,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brotorp, Långsjön, Sm</t>
+          <t>Brotorp, hyggeskant, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575795</v>
+        <v>575654</v>
       </c>
       <c r="R7" t="n">
-        <v>6404519</v>
+        <v>6404507</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1349,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
@@ -1369,43 +1369,43 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111837705</t>
+          <t>https://artportalen.se/Sighting/111837741</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96263359</v>
+        <v>111837705</v>
       </c>
       <c r="B8" t="n">
-        <v>93197</v>
+        <v>93193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1417,14 +1417,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brotorp S, Hummelstad, Sm</t>
+          <t>Brotorp, Långsjön, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575780</v>
+        <v>575795</v>
       </c>
       <c r="R8" t="n">
-        <v>6404610</v>
+        <v>6404519</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,34 +1451,19 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>50+30 fruktkroppar vid två tallar.</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
@@ -1498,13 +1483,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96263359</t>
+          <t>https://artportalen.se/Sighting/111837705</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96557117</v>
+        <v>96263359</v>
       </c>
       <c r="B9" t="n">
         <v>93197</v>
@@ -1534,7 +1519,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1546,14 +1531,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Brotorpsskogen, Sm</t>
+          <t>Brotorp S, Hummelstad, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575771</v>
+        <v>575780</v>
       </c>
       <c r="R9" t="n">
-        <v>6404547</v>
+        <v>6404610</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,12 +1565,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-10-09</t>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-09</t>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>50+30 fruktkroppar vid två tallar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,13 +1612,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96557117</t>
+          <t>https://artportalen.se/Sighting/96263359</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112360057</v>
+        <v>96557117</v>
       </c>
       <c r="B10" t="n">
         <v>93197</v>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1660,14 +1660,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Brotorp, Hummelstad, Sm</t>
+          <t>Brotorpsskogen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
         <v>575771</v>
       </c>
       <c r="R10" t="n">
-        <v>6404602</v>
+        <v>6404547</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1694,12 +1694,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2021-10-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2021-10-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1726,62 +1726,62 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112360057</t>
+          <t>https://artportalen.se/Sighting/96557117</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105344960</v>
+        <v>112360057</v>
       </c>
       <c r="B11" t="n">
-        <v>91893</v>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4660</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 54601, Brotorp, Sm</t>
+          <t>Brotorp, Hummelstad, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575585</v>
+        <v>575771</v>
       </c>
       <c r="R11" t="n">
-        <v>6404590</v>
+        <v>6404602</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1808,17 +1808,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-12-25</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-12-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På liggande död asp.</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,62 +1840,62 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105344960</t>
+          <t>https://artportalen.se/Sighting/112360057</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96263315</v>
+        <v>105344960</v>
       </c>
       <c r="B12" t="n">
-        <v>93233</v>
+        <v>91893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>4660</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brotorp S, Hummelstad, Sm</t>
+          <t>A 54601, Brotorp, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575746</v>
+        <v>575585</v>
       </c>
       <c r="R12" t="n">
-        <v>6404546</v>
+        <v>6404590</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,22 +1922,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2022-12-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2022-12-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På liggande död asp.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1969,45 +1959,41 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96263315</t>
+          <t>https://artportalen.se/Sighting/105344960</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96557108</v>
+        <v>137399399</v>
       </c>
       <c r="B13" t="n">
-        <v>93233</v>
+        <v>92153</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>4660</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -2017,14 +2003,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Brotorpsskogen, Sm</t>
+          <t>Brotorp, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575771</v>
+        <v>575762</v>
       </c>
       <c r="R13" t="n">
-        <v>6404547</v>
+        <v>6404638</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2051,12 +2037,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-10-09</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-10-09</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2083,66 +2069,65 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96557108</t>
+          <t>https://artportalen.se/Sighting/137399399</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>91774594</v>
+        <v>96263315</v>
       </c>
       <c r="B14" t="n">
-        <v>57247</v>
+        <v>93233</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100038</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hummelstad, Brotorp, Sm</t>
+          <t>Brotorp S, Hummelstad, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575763</v>
+        <v>575746</v>
       </c>
       <c r="R14" t="n">
-        <v>6404600</v>
+        <v>6404546</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2166,12 +2151,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-03-22</t>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-03-22</t>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2180,6 +2175,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2191,22 +2187,22 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91774594</t>
+          <t>https://artportalen.se/Sighting/96263315</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>91218403</v>
+        <v>96557108</v>
       </c>
       <c r="B15" t="n">
-        <v>57966</v>
+        <v>93233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2214,21 +2210,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100048</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2236,27 +2232,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hummelstad, Brotorp, Sm</t>
+          <t>Brotorpsskogen, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575763</v>
+        <v>575771</v>
       </c>
       <c r="R15" t="n">
-        <v>6404600</v>
+        <v>6404547</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2280,17 +2275,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-02-27</t>
+          <t>2021-10-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-02-27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Intensivt trummande i dungen morg/fm</t>
+          <t>2021-10-09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,6 +2289,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2310,22 +2301,22 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91218403</t>
+          <t>https://artportalen.se/Sighting/96557108</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>91774603</v>
+        <v>91774594</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>57247</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,21 +2324,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100038</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2424,39 +2415,39 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91774603</t>
+          <t>https://artportalen.se/Sighting/91774594</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>97695128</v>
+        <v>91218403</v>
       </c>
       <c r="B17" t="n">
-        <v>57950</v>
+        <v>57966</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2473,23 +2464,23 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Brotorpsskogen, Sm</t>
+          <t>Hummelstad, Brotorp, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575762</v>
+        <v>575763</v>
       </c>
       <c r="R17" t="n">
-        <v>6404578</v>
+        <v>6404600</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2513,12 +2504,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-12-25</t>
+          <t>2021-02-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-12-25</t>
+          <t>2021-02-27</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Intensivt trummande i dungen morg/fm</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2538,22 +2534,22 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97695128</t>
+          <t>https://artportalen.se/Sighting/91218403</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>97964712</v>
+        <v>91774603</v>
       </c>
       <c r="B18" t="n">
-        <v>57899</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2561,16 +2557,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100067</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2587,23 +2583,23 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brotorpsskogen, Sm</t>
+          <t>Hummelstad, Brotorp, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575682</v>
+        <v>575763</v>
       </c>
       <c r="R18" t="n">
-        <v>6404524</v>
+        <v>6404600</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2627,12 +2623,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-01-07</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-01-07</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2658,38 +2654,38 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97964712</t>
+          <t>https://artportalen.se/Sighting/91774603</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>94255908</v>
+        <v>97695128</v>
       </c>
       <c r="B19" t="n">
-        <v>57942</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102119</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2701,23 +2697,23 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hummelstad, Brotorp, Sm</t>
+          <t>Brotorpsskogen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575763</v>
+        <v>575762</v>
       </c>
       <c r="R19" t="n">
-        <v>6404600</v>
+        <v>6404578</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2741,22 +2737,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-06-14</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>02:15</t>
+          <t>2021-12-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-06-14</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>02:15</t>
+          <t>2021-12-25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2782,16 +2768,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94255908</t>
+          <t>https://artportalen.se/Sighting/97695128</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121659150</v>
+        <v>97964712</v>
       </c>
       <c r="B20" t="n">
-        <v>58327</v>
+        <v>57899</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,16 +2785,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>100067</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2816,21 +2802,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A 54601, Brotorp, Sm</t>
+          <t>Brotorpsskogen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575628</v>
+        <v>575682</v>
       </c>
       <c r="R20" t="n">
-        <v>6404582</v>
+        <v>6404524</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2857,12 +2851,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2022-01-07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2022-01-07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2888,63 +2882,66 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121659150</t>
+          <t>https://artportalen.se/Sighting/97964712</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>116466731</v>
+        <v>94255908</v>
       </c>
       <c r="B21" t="n">
-        <v>56884</v>
+        <v>57942</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>208255</v>
+        <v>102119</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>A 54601, Brotorp, Sm</t>
+          <t>Hummelstad, Brotorp, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575628</v>
+        <v>575763</v>
       </c>
       <c r="R21" t="n">
-        <v>6404582</v>
+        <v>6404600</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2968,12 +2965,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2021-06-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>02:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2021-06-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>02:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2982,7 +2989,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3000,16 +3006,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116466731</t>
+          <t>https://artportalen.se/Sighting/94255908</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111837675</v>
+        <v>121659150</v>
       </c>
       <c r="B22" t="n">
-        <v>106244</v>
+        <v>58327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3017,46 +3023,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brotorp, Långsjön, Sm</t>
+          <t>A 54601, Brotorp, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575782</v>
+        <v>575628</v>
       </c>
       <c r="R22" t="n">
-        <v>6404547</v>
+        <v>6404582</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3083,12 +3081,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3097,7 +3095,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3115,16 +3112,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111837675</t>
+          <t>https://artportalen.se/Sighting/121659150</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112360070</v>
+        <v>116466731</v>
       </c>
       <c r="B23" t="n">
-        <v>106244</v>
+        <v>56884</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3132,42 +3129,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>208255</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brotorp, Hummelstad, Sm</t>
+          <t>A 54601, Brotorp, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575771</v>
+        <v>575628</v>
       </c>
       <c r="R23" t="n">
-        <v>6404602</v>
+        <v>6404582</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3194,17 +3192,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Få</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3231,59 +3224,63 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112360070</t>
+          <t>https://artportalen.se/Sighting/116466731</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>116468450</v>
+        <v>111837675</v>
       </c>
       <c r="B24" t="n">
-        <v>99754</v>
+        <v>106244</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222295</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Latourr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Brotorp, Hummelstad, Sm</t>
+          <t>Brotorp, Långsjön, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575599</v>
+        <v>575782</v>
       </c>
       <c r="R24" t="n">
-        <v>6404549</v>
+        <v>6404547</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3310,17 +3307,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Få, igenväxande beteshage. På samma ställe där slåttergubbe växte för många år sedan-</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3346,6 +3338,238 @@
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111837675</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>112360070</v>
+      </c>
+      <c r="B25" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Brotorp, Hummelstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>575771</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6404602</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Få</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112360070</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>116468450</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Brotorp, Hummelstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>575599</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6404549</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Få, igenväxande beteshage. På samma ställe där slåttergubbe växte för många år sedan-</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/116468450</t>
         </is>
@@ -3376,6 +3600,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54601-2022 artfynd.xlsx
+++ b/artfynd/A 54601-2022 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>137398924</v>
       </c>
       <c r="B3" t="n">
-        <v>92969</v>
+        <v>92981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137399399</v>
       </c>
       <c r="B13" t="n">
-        <v>92153</v>
+        <v>92165</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 54601-2022 artfynd.xlsx
+++ b/artfynd/A 54601-2022 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>137398924</v>
       </c>
       <c r="B3" t="n">
-        <v>92981</v>
+        <v>92982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137399399</v>
       </c>
       <c r="B13" t="n">
-        <v>92165</v>
+        <v>92166</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 54601-2022 artfynd.xlsx
+++ b/artfynd/A 54601-2022 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>137398924</v>
       </c>
       <c r="B3" t="n">
-        <v>92982</v>
+        <v>92985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137399399</v>
       </c>
       <c r="B13" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 54601-2022 artfynd.xlsx
+++ b/artfynd/A 54601-2022 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>137398924</v>
       </c>
       <c r="B3" t="n">
-        <v>92985</v>
+        <v>92989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137399399</v>
       </c>
       <c r="B13" t="n">
-        <v>92169</v>
+        <v>92173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
